--- a/data/trans_bre/P1423-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1423-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,7; 12,12</t>
+          <t>3,12; 12,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 12,57</t>
+          <t>2,8; 12,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,4; 14,88</t>
+          <t>4,45; 15,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 5,6</t>
+          <t>1,09; 5,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>75,6; 825,91</t>
+          <t>66,24; 768,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,24; 393,21</t>
+          <t>37,72; 375,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,72; 516,47</t>
+          <t>48,6; 463,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32,54; 790,06</t>
+          <t>19,38; 657,72</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,96; 9,59</t>
+          <t>3,67; 9,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,97; 12,46</t>
+          <t>5,17; 12,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,68; 9,9</t>
+          <t>3,7; 9,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,3; 11,03</t>
+          <t>4,53; 11,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>107,77; 695,66</t>
+          <t>93,55; 601,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,53; 533,73</t>
+          <t>81,47; 497,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,49; 500,46</t>
+          <t>83,15; 511,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>54,59; 284,07</t>
+          <t>54,6; 290,91</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 8,52</t>
+          <t>2,73; 8,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,79; 10,67</t>
+          <t>1,77; 10,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 10,33</t>
+          <t>3,71; 9,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 10,9</t>
+          <t>2,06; 10,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>41,3; 2240,38</t>
+          <t>65,17; 2146,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,99; 294,27</t>
+          <t>21,02; 290,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>108,99; 2351,32</t>
+          <t>112,57; 2414,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,41; 171,7</t>
+          <t>14,66; 162,01</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 5,33</t>
+          <t>-0,26; 4,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,37; 14,86</t>
+          <t>7,46; 14,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 7,0</t>
+          <t>0,72; 7,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 4,09</t>
+          <t>-4,89; 4,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 486,44</t>
+          <t>-15,07; 461,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>168,0; 1200,42</t>
+          <t>161,81; 1106,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,37; 406,15</t>
+          <t>6,82; 439,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-49,65; 68,91</t>
+          <t>-45,64; 73,21</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,96; 12,12</t>
+          <t>2,8; 12,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,34; 22,09</t>
+          <t>9,82; 22,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,85; 12,87</t>
+          <t>2,14; 13,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 7,74</t>
+          <t>0,79; 7,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,28; 690,22</t>
+          <t>35,93; 606,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>123,69; 782,87</t>
+          <t>114,39; 735,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,71; 401,4</t>
+          <t>23,07; 382,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,63; 1100,37</t>
+          <t>19,34; 1041,58</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,15; 8,09</t>
+          <t>2,1; 7,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,88; 12,69</t>
+          <t>3,44; 12,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,16; 14,7</t>
+          <t>6,14; 14,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,17; 9,86</t>
+          <t>-0,36; 9,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>62,97; —</t>
+          <t>40,03; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,55; 375,41</t>
+          <t>43,29; 424,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>133,97; 1157,69</t>
+          <t>143,15; 1232,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,75; 122,98</t>
+          <t>-5,13; 113,28</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,56; 7,72</t>
+          <t>2,58; 7,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 6,78</t>
+          <t>1,17; 6,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,87; 8,83</t>
+          <t>4,06; 9,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 9,16</t>
+          <t>-1,82; 9,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>55,11; 378,41</t>
+          <t>60,02; 371,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,14; 173,63</t>
+          <t>14,22; 172,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>108,94; 620,41</t>
+          <t>116,71; 635,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-28,46; 143,35</t>
+          <t>-21,4; 138,68</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 4,45</t>
+          <t>-0,86; 4,34</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,21; 7,82</t>
+          <t>3,32; 8,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,64; 10,18</t>
+          <t>4,44; 10,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,34; 11,34</t>
+          <t>5,47; 11,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 100,95</t>
+          <t>-13,32; 95,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>69,9; 359,48</t>
+          <t>81,22; 397,59</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>86,6; 307,86</t>
+          <t>84,2; 325,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>94,17; 574,9</t>
+          <t>104,24; 640,67</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,44; 5,61</t>
+          <t>3,4; 5,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,83; 8,42</t>
+          <t>6,01; 8,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,78; 8,11</t>
+          <t>5,78; 8,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,19; 6,9</t>
+          <t>3,37; 7,03</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>96,3; 209,38</t>
+          <t>95,87; 207,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>121,93; 235,6</t>
+          <t>129,22; 239,44</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>156,24; 293,11</t>
+          <t>153,38; 285,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>54,36; 143,15</t>
+          <t>56,85; 149,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P1423-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1423-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,3</t>
+          <t>3,45</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>187,77%</t>
+          <t>216,75%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 12,36</t>
+          <t>3,8; 12,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 12,07</t>
+          <t>2,93; 12,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,45; 15,18</t>
+          <t>4,95; 15,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 5,55</t>
+          <t>1,34; 5,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>66,24; 768,36</t>
+          <t>89,44; 861,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,72; 375,56</t>
+          <t>34,78; 358,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,6; 463,5</t>
+          <t>63,46; 505,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,38; 657,72</t>
+          <t>34,77; 806,1</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>144,41%</t>
+          <t>139,42%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,67; 9,46</t>
+          <t>3,8; 9,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,17; 12,35</t>
+          <t>4,86; 12,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,7; 9,88</t>
+          <t>3,65; 10,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,53; 11,36</t>
+          <t>4,43; 11,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>93,55; 601,44</t>
+          <t>79,56; 618,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,47; 497,05</t>
+          <t>72,64; 584,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,15; 511,9</t>
+          <t>79,36; 482,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>54,6; 290,91</t>
+          <t>48,63; 279,71</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,5</t>
+          <t>5,99</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>65,28%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,73; 8,68</t>
+          <t>2,58; 8,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 10,77</t>
+          <t>1,82; 11,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,71; 9,95</t>
+          <t>3,58; 10,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 10,62</t>
+          <t>1,71; 9,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>65,17; 2146,56</t>
+          <t>33,6; 2256,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,02; 290,81</t>
+          <t>19,07; 346,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>112,57; 2414,11</t>
+          <t>112,06; 2607,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,66; 162,01</t>
+          <t>10,56; 140,56</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,16</t>
+          <t>2,68</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>37,57%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 4,96</t>
+          <t>-0,17; 4,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,46; 14,87</t>
+          <t>7,11; 14,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 7,06</t>
+          <t>0,84; 6,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 4,49</t>
+          <t>-1,44; 6,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 461,54</t>
+          <t>-16,61; 457,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>161,81; 1106,73</t>
+          <t>129,23; 1120,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,82; 439,39</t>
+          <t>10,52; 389,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-45,64; 73,21</t>
+          <t>-17,49; 131,03</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,55</t>
+          <t>5,91</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>272,44%</t>
+          <t>387,42%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,8; 12,52</t>
+          <t>2,34; 12,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,82; 22,0</t>
+          <t>9,32; 22,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,14; 13,07</t>
+          <t>2,07; 13,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 7,88</t>
+          <t>3,28; 8,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,93; 606,35</t>
+          <t>27,18; 700,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>114,39; 735,89</t>
+          <t>112,06; 772,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,07; 382,49</t>
+          <t>20,22; 391,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,34; 1041,58</t>
+          <t>95,7; 1408,27</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,91</t>
+          <t>4,78</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>47,19%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,1; 7,91</t>
+          <t>2,25; 8,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,44; 12,9</t>
+          <t>3,33; 13,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,14; 14,83</t>
+          <t>5,62; 14,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 9,22</t>
+          <t>-0,13; 9,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40,03; —</t>
+          <t>70,62; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>43,29; 424,07</t>
+          <t>35,69; 428,34</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>143,15; 1232,32</t>
+          <t>133,66; 1352,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 113,28</t>
+          <t>-1,72; 113,65</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,33</t>
+          <t>7,77</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>106,54%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,58; 7,68</t>
+          <t>2,7; 7,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 6,62</t>
+          <t>1,01; 6,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,06; 9,19</t>
+          <t>3,63; 8,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 9,1</t>
+          <t>4,67; 10,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>60,02; 371,51</t>
+          <t>65,58; 355,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,22; 172,02</t>
+          <t>15,4; 174,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>116,71; 635,06</t>
+          <t>104,67; 607,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-21,4; 138,68</t>
+          <t>48,03; 193,55</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7,89</t>
+          <t>6,6</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>208,18%</t>
+          <t>129,13%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 4,34</t>
+          <t>-0,93; 4,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,32; 8,17</t>
+          <t>3,01; 7,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,44; 10,12</t>
+          <t>4,73; 10,2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,47; 11,35</t>
+          <t>4,12; 8,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 95,11</t>
+          <t>-14,19; 87,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>81,22; 397,59</t>
+          <t>69,71; 366,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,2; 325,08</t>
+          <t>90,52; 315,5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>104,24; 640,67</t>
+          <t>56,77; 221,01</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5,42</t>
+          <t>6,13</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>100,74%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,4; 5,59</t>
+          <t>3,38; 5,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,01; 8,55</t>
+          <t>5,94; 8,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,78; 8,17</t>
+          <t>5,69; 8,08</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,37; 7,03</t>
+          <t>4,9; 7,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>95,87; 207,45</t>
+          <t>94,2; 210,06</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>129,22; 239,44</t>
+          <t>125,35; 236,43</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>153,38; 285,53</t>
+          <t>154,23; 286,66</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>56,85; 149,75</t>
+          <t>71,33; 133,31</t>
         </is>
       </c>
     </row>
